--- a/artfynd/A 33853-2022 artfynd.xlsx
+++ b/artfynd/A 33853-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101253632</v>
+        <v>134259740</v>
       </c>
       <c r="B2" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>102987</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartbäcken, Srm</t>
+          <t>Svarvarbäcken, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587512.4021594548</v>
+        <v>587471</v>
       </c>
       <c r="R2" t="n">
-        <v>6549033.844268398</v>
+        <v>6549012</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,61 +772,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägren</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Michael Löfroth</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Michael Löfroth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101263117</v>
+        <v>101253632</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>221317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587512.4021594548</v>
+        <v>587512</v>
       </c>
       <c r="R3" t="n">
-        <v>6549033.844268398</v>
+        <v>6549034</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +862,9 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,6 +877,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -911,6 +894,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101263117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587512</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6549034</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33853-2022 artfynd.xlsx
+++ b/artfynd/A 33853-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134259740</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101253632</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101263117</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>